--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6584" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6584" uniqueCount="796">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:27:45+00:00</t>
+    <t>2025-02-12T10:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -465,22 +465,19 @@
 </t>
   </si>
   <si>
-    <t>A recorded sex or gender property for the individual</t>
-  </si>
-  <si>
     <t>Additional notes that apply to this resource or element.</t>
   </si>
   <si>
     <t>This extension SHALL NOT be used if the resource already has standard 'note' element (or equivalent) of type Annotation on the same element</t>
   </si>
   <si>
-    <t>Claim.extension:DiagnosisRelatedNode</t>
-  </si>
-  <si>
-    <t>DiagnosisRelatedNode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-diagnosisRelatedNode}
+    <t>Claim.extension:DiagnoseKnoten</t>
+  </si>
+  <si>
+    <t>DiagnoseKnoten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-diagnoseKnoten}
 </t>
   </si>
   <si>
@@ -493,7 +490,7 @@
     <t>LKFPunkte</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/lkfPunkte}
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-LKFPunkte}
 </t>
   </si>
   <si>
@@ -503,13 +500,13 @@
     <t>In dieser Extension werden alle möglichen Punkteangaben im LKF zusammengefasst.</t>
   </si>
   <si>
-    <t>Claim.extension:ErrorWarning</t>
-  </si>
-  <si>
-    <t>ErrorWarning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-ErrorWarning}
+    <t>Claim.extension:FehlerWarnung</t>
+  </si>
+  <si>
+    <t>FehlerWarnung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-fehlerWarnung}
 </t>
   </si>
   <si>
@@ -1164,13 +1161,13 @@
 </t>
   </si>
   <si>
-    <t>Claim.encounter:MopedEncounterKH</t>
-  </si>
-  <si>
-    <t>MopedEncounterKH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedEncounterKH)
+    <t>Claim.encounter:MopedEncounter</t>
+  </si>
+  <si>
+    <t>MopedEncounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedEncounter)
 </t>
   </si>
   <si>
@@ -3863,10 +3860,10 @@
         <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="N10" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3942,13 +3939,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>19</v>
@@ -3970,13 +3967,13 @@
         <v>19</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>150</v>
-      </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -4053,13 +4050,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>19</v>
@@ -4081,13 +4078,13 @@
         <v>19</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -4164,13 +4161,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>19</v>
@@ -4192,13 +4189,13 @@
         <v>19</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -4275,13 +4272,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>19</v>
@@ -4303,13 +4300,13 @@
         <v>19</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4386,13 +4383,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>19</v>
@@ -4414,13 +4411,13 @@
         <v>19</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4497,13 +4494,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>19</v>
@@ -4525,13 +4522,13 @@
         <v>19</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4608,14 +4605,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4637,16 +4634,16 @@
         <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>19</v>
@@ -4695,7 +4692,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -4721,14 +4718,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4747,17 +4744,17 @@
         <v>19</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>19</v>
@@ -4806,7 +4803,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4821,10 +4818,10 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>19</v>
@@ -4832,10 +4829,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4858,17 +4855,17 @@
         <v>19</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>19</v>
@@ -4917,7 +4914,7 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4943,10 +4940,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4972,16 +4969,16 @@
         <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>19</v>
@@ -5009,11 +5006,11 @@
         <v>111</v>
       </c>
       <c r="Y20" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z20" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>199</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>19</v>
       </c>
@@ -5030,7 +5027,7 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>87</v>
@@ -5045,10 +5042,10 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>19</v>
@@ -5056,10 +5053,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5082,19 +5079,19 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>19</v>
@@ -5104,29 +5101,29 @@
         <v>19</v>
       </c>
       <c r="S21" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X21" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="T21" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X21" t="s" s="2">
+      <c r="Y21" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y21" t="s" s="2">
+      <c r="Z21" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Z21" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="AA21" t="s" s="2">
         <v>19</v>
       </c>
@@ -5143,7 +5140,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>87</v>
@@ -5161,7 +5158,7 @@
         <v>19</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>19</v>
@@ -5169,10 +5166,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5195,19 +5192,19 @@
         <v>19</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>19</v>
@@ -5232,14 +5229,14 @@
         <v>19</v>
       </c>
       <c r="X22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="Y22" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="Y22" t="s" s="2">
+      <c r="Z22" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="Z22" t="s" s="2">
-        <v>220</v>
-      </c>
       <c r="AA22" t="s" s="2">
         <v>19</v>
       </c>
@@ -5256,7 +5253,7 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -5274,7 +5271,7 @@
         <v>19</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>19</v>
@@ -5282,10 +5279,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5311,14 +5308,14 @@
         <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>19</v>
@@ -5328,7 +5325,7 @@
         <v>19</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>19</v>
@@ -5346,11 +5343,11 @@
         <v>111</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="Z23" t="s" s="2">
-        <v>227</v>
-      </c>
       <c r="AA23" t="s" s="2">
         <v>19</v>
       </c>
@@ -5367,7 +5364,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>87</v>
@@ -5385,7 +5382,7 @@
         <v>19</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>19</v>
@@ -5393,10 +5390,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5419,17 +5416,17 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>19</v>
@@ -5478,7 +5475,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>87</v>
@@ -5493,10 +5490,10 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>19</v>
@@ -5504,10 +5501,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5530,19 +5527,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>19</v>
@@ -5591,7 +5588,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -5609,7 +5606,7 @@
         <v>19</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>19</v>
@@ -5617,10 +5614,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5643,19 +5640,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>19</v>
@@ -5704,7 +5701,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>87</v>
@@ -5719,10 +5716,10 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>19</v>
@@ -5730,10 +5727,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5756,17 +5753,17 @@
         <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
@@ -5815,7 +5812,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -5833,7 +5830,7 @@
         <v>19</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>19</v>
@@ -5841,10 +5838,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5867,13 +5864,13 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5924,7 +5921,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -5939,7 +5936,7 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>19</v>
@@ -5950,10 +5947,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5976,16 +5973,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6035,7 +6032,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -6050,10 +6047,10 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>19</v>
@@ -6061,10 +6058,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6087,19 +6084,19 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
@@ -6124,14 +6121,14 @@
         <v>19</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>19</v>
       </c>
@@ -6148,7 +6145,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -6163,7 +6160,7 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>19</v>
@@ -6174,14 +6171,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6200,19 +6197,19 @@
         <v>19</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -6237,14 +6234,14 @@
         <v>19</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>19</v>
       </c>
@@ -6261,7 +6258,7 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -6287,10 +6284,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6313,19 +6310,19 @@
         <v>19</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>19</v>
@@ -6374,7 +6371,7 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -6400,10 +6397,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6426,13 +6423,13 @@
         <v>19</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6483,40 +6480,40 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI33" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI33" t="s" s="2">
+      <c r="AJ33" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6538,13 +6535,13 @@
         <v>134</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="N34" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6594,7 +6591,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6615,19 +6612,19 @@
         <v>19</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6649,16 +6646,16 @@
         <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N35" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>19</v>
@@ -6707,7 +6704,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6733,10 +6730,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6759,17 +6756,17 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6818,7 +6815,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6833,7 +6830,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>19</v>
@@ -6844,10 +6841,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6870,19 +6867,19 @@
         <v>19</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6907,14 +6904,14 @@
         <v>19</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>316</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>19</v>
       </c>
@@ -6931,7 +6928,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6957,10 +6954,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6983,19 +6980,19 @@
         <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>19</v>
@@ -7044,7 +7041,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -7070,10 +7067,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7096,17 +7093,17 @@
         <v>19</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>19</v>
@@ -7155,7 +7152,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -7181,10 +7178,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7207,19 +7204,19 @@
         <v>19</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>19</v>
@@ -7268,7 +7265,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -7294,10 +7291,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7320,19 +7317,19 @@
         <v>19</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>19</v>
@@ -7381,7 +7378,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -7407,10 +7404,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7433,13 +7430,13 @@
         <v>19</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7490,40 +7487,40 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI42" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI42" t="s" s="2">
+      <c r="AJ42" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7545,13 +7542,13 @@
         <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="N43" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7601,7 +7598,7 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7622,19 +7619,19 @@
         <v>19</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7656,16 +7653,16 @@
         <v>134</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N44" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>19</v>
@@ -7714,7 +7711,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7740,10 +7737,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7766,17 +7763,17 @@
         <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7801,14 +7798,14 @@
         <v>19</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>19</v>
       </c>
@@ -7825,7 +7822,7 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>87</v>
@@ -7851,10 +7848,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7877,19 +7874,19 @@
         <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>19</v>
@@ -7938,7 +7935,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7964,10 +7961,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7990,19 +7987,19 @@
         <v>19</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -8051,7 +8048,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -8069,7 +8066,7 @@
         <v>19</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>19</v>
@@ -8077,10 +8074,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8103,19 +8100,19 @@
         <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -8152,7 +8149,7 @@
         <v>19</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
@@ -8162,7 +8159,7 @@
         <v>138</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -8188,13 +8185,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C49" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>19</v>
@@ -8216,19 +8213,19 @@
         <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L49" t="s" s="2">
-        <v>369</v>
-      </c>
       <c r="M49" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -8277,7 +8274,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -8303,13 +8300,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C50" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>19</v>
@@ -8331,19 +8328,19 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L50" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="M50" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -8392,7 +8389,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8418,10 +8415,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8444,17 +8441,17 @@
         <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -8503,7 +8500,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8521,7 +8518,7 @@
         <v>19</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>19</v>
@@ -8529,10 +8526,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8555,19 +8552,19 @@
         <v>19</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -8596,7 +8593,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -8614,7 +8611,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -8640,10 +8637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8666,13 +8663,13 @@
         <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8723,7 +8720,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -8749,10 +8746,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8775,13 +8772,13 @@
         <v>19</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8832,40 +8829,40 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI54" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI54" t="s" s="2">
+      <c r="AJ54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8887,13 +8884,13 @@
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="N55" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8943,7 +8940,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8964,19 +8961,19 @@
         <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8998,16 +8995,16 @@
         <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N56" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>19</v>
@@ -9056,7 +9053,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -9082,10 +9079,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9108,13 +9105,13 @@
         <v>19</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9141,11 +9138,11 @@
         <v>19</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>19</v>
@@ -9163,7 +9160,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>87</v>
@@ -9189,10 +9186,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9215,13 +9212,13 @@
         <v>19</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9272,7 +9269,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>87</v>
@@ -9298,10 +9295,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9324,17 +9321,17 @@
         <v>19</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -9383,7 +9380,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9409,10 +9406,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9435,13 +9432,13 @@
         <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9492,40 +9489,40 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI60" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI60" t="s" s="2">
+      <c r="AJ60" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9547,13 +9544,13 @@
         <v>134</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="N61" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9603,7 +9600,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9624,19 +9621,19 @@
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9658,16 +9655,16 @@
         <v>134</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N62" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O62" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>19</v>
@@ -9716,7 +9713,7 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9742,10 +9739,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9768,17 +9765,17 @@
         <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>19</v>
@@ -9827,7 +9824,7 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>87</v>
@@ -9853,10 +9850,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9879,17 +9876,17 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>19</v>
@@ -9938,7 +9935,7 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>87</v>
@@ -9956,7 +9953,7 @@
         <v>19</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>19</v>
@@ -9964,10 +9961,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9990,19 +9987,19 @@
         <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
@@ -10051,7 +10048,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -10077,10 +10074,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10103,19 +10100,19 @@
         <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>19</v>
@@ -10140,14 +10137,14 @@
         <v>19</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>19</v>
       </c>
@@ -10164,7 +10161,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -10190,10 +10187,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10216,17 +10213,17 @@
         <v>19</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>19</v>
@@ -10251,11 +10248,11 @@
         <v>19</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>19</v>
@@ -10273,7 +10270,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10299,14 +10296,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10325,19 +10322,19 @@
         <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -10386,7 +10383,7 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10401,7 +10398,7 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>19</v>
@@ -10412,10 +10409,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10438,13 +10435,13 @@
         <v>19</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10495,40 +10492,40 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI69" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI69" t="s" s="2">
+      <c r="AJ69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10550,13 +10547,13 @@
         <v>134</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="N70" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10606,7 +10603,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10627,19 +10624,19 @@
         <v>19</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10661,16 +10658,16 @@
         <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N71" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O71" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -10719,7 +10716,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10745,10 +10742,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10771,17 +10768,17 @@
         <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -10830,7 +10827,7 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>87</v>
@@ -10856,10 +10853,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10882,19 +10879,19 @@
         <v>19</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>19</v>
@@ -10919,14 +10916,14 @@
         <v>19</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>456</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>19</v>
       </c>
@@ -10943,7 +10940,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>87</v>
@@ -10969,10 +10966,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10995,17 +10992,17 @@
         <v>19</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>19</v>
@@ -11030,14 +11027,14 @@
         <v>19</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>462</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>19</v>
       </c>
@@ -11054,7 +11051,7 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -11080,10 +11077,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11106,13 +11103,13 @@
         <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11163,7 +11160,7 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -11189,10 +11186,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11215,19 +11212,19 @@
         <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>19</v>
@@ -11276,7 +11273,7 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -11302,10 +11299,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11328,19 +11325,19 @@
         <v>19</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>19</v>
@@ -11365,14 +11362,14 @@
         <v>19</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>19</v>
       </c>
@@ -11389,7 +11386,7 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -11415,10 +11412,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11441,17 +11438,17 @@
         <v>19</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>19</v>
@@ -11500,7 +11497,7 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11515,7 +11512,7 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>19</v>
@@ -11526,10 +11523,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11552,13 +11549,13 @@
         <v>19</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11609,40 +11606,40 @@
         <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI79" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG79" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI79" t="s" s="2">
+      <c r="AJ79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11664,13 +11661,13 @@
         <v>134</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M80" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="N80" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11720,7 +11717,7 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11741,19 +11738,19 @@
         <v>19</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11775,16 +11772,16 @@
         <v>134</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M81" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N81" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O81" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>19</v>
@@ -11833,7 +11830,7 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11859,10 +11856,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11885,19 +11882,19 @@
         <v>19</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>19</v>
@@ -11946,7 +11943,7 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>87</v>
@@ -11972,10 +11969,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11998,17 +11995,17 @@
         <v>19</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>19</v>
@@ -12033,14 +12030,14 @@
         <v>19</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="Z83" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="AA83" t="s" s="2">
         <v>19</v>
       </c>
@@ -12057,7 +12054,7 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>87</v>
@@ -12083,10 +12080,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12109,19 +12106,19 @@
         <v>19</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>19</v>
@@ -12146,14 +12143,14 @@
         <v>19</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>19</v>
       </c>
@@ -12170,7 +12167,7 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -12196,10 +12193,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12222,17 +12219,17 @@
         <v>19</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>19</v>
@@ -12257,14 +12254,14 @@
         <v>19</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>512</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>19</v>
       </c>
@@ -12281,7 +12278,7 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -12307,10 +12304,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12333,17 +12330,17 @@
         <v>19</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>19</v>
@@ -12392,7 +12389,7 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -12418,10 +12415,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12444,13 +12441,13 @@
         <v>19</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12501,36 +12498,36 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI87" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI87" t="s" s="2">
+      <c r="AJ87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12608,7 +12605,7 @@
         <v>138</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12634,13 +12631,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C89" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>19</v>
@@ -12662,13 +12659,13 @@
         <v>19</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12719,7 +12716,7 @@
         <v>19</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12745,14 +12742,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12774,16 +12771,16 @@
         <v>134</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N90" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O90" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>19</v>
@@ -12832,7 +12829,7 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12858,10 +12855,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12884,17 +12881,17 @@
         <v>19</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>19</v>
@@ -12943,7 +12940,7 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>87</v>
@@ -12969,10 +12966,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12995,19 +12992,19 @@
         <v>19</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M92" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>531</v>
-      </c>
       <c r="O92" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>19</v>
@@ -13032,14 +13029,14 @@
         <v>19</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>533</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>19</v>
       </c>
@@ -13056,7 +13053,7 @@
         <v>19</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -13082,10 +13079,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13108,17 +13105,17 @@
         <v>19</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>19</v>
@@ -13167,7 +13164,7 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -13193,10 +13190,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13219,17 +13216,17 @@
         <v>19</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>19</v>
@@ -13254,14 +13251,14 @@
         <v>19</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>544</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>19</v>
       </c>
@@ -13278,7 +13275,7 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>87</v>
@@ -13304,10 +13301,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13330,17 +13327,17 @@
         <v>19</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>19</v>
@@ -13389,7 +13386,7 @@
         <v>19</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13415,10 +13412,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13441,19 +13438,19 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>19</v>
@@ -13502,7 +13499,7 @@
         <v>19</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13523,15 +13520,15 @@
         <v>19</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13554,13 +13551,13 @@
         <v>19</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13611,40 +13608,40 @@
         <v>19</v>
       </c>
       <c r="AF97" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI97" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI97" t="s" s="2">
+      <c r="AJ97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM97" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13666,13 +13663,13 @@
         <v>134</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M98" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="N98" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13722,7 +13719,7 @@
         <v>19</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13743,19 +13740,19 @@
         <v>19</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13777,16 +13774,16 @@
         <v>134</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M99" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N99" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O99" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>19</v>
@@ -13835,7 +13832,7 @@
         <v>19</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -13861,10 +13858,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13887,17 +13884,17 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>19</v>
@@ -13946,7 +13943,7 @@
         <v>19</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>87</v>
@@ -13972,10 +13969,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13998,19 +13995,19 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>19</v>
@@ -14059,7 +14056,7 @@
         <v>19</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>87</v>
@@ -14085,10 +14082,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14111,19 +14108,19 @@
         <v>19</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>19</v>
@@ -14172,7 +14169,7 @@
         <v>19</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -14187,10 +14184,10 @@
         <v>99</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AL102" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>19</v>
@@ -14198,10 +14195,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14224,17 +14221,17 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>19</v>
@@ -14283,7 +14280,7 @@
         <v>19</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>87</v>
@@ -14309,10 +14306,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14335,17 +14332,17 @@
         <v>19</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>19</v>
@@ -14394,7 +14391,7 @@
         <v>19</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -14420,10 +14417,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14446,19 +14443,19 @@
         <v>19</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>19</v>
@@ -14507,7 +14504,7 @@
         <v>19</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -14533,10 +14530,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14559,19 +14556,19 @@
         <v>19</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>19</v>
@@ -14620,7 +14617,7 @@
         <v>19</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -14646,10 +14643,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14672,17 +14669,17 @@
         <v>19</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>19</v>
@@ -14731,7 +14728,7 @@
         <v>19</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14757,10 +14754,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14783,13 +14780,13 @@
         <v>19</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14840,40 +14837,40 @@
         <v>19</v>
       </c>
       <c r="AF108" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI108" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG108" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI108" t="s" s="2">
+      <c r="AJ108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM108" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -14895,13 +14892,13 @@
         <v>134</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M109" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="N109" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14951,7 +14948,7 @@
         <v>19</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14972,19 +14969,19 @@
         <v>19</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15006,16 +15003,16 @@
         <v>134</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M110" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N110" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O110" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>19</v>
@@ -15064,7 +15061,7 @@
         <v>19</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -15090,10 +15087,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15116,19 +15113,19 @@
         <v>19</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>19</v>
@@ -15177,7 +15174,7 @@
         <v>19</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>87</v>
@@ -15203,10 +15200,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15229,17 +15226,17 @@
         <v>19</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>19</v>
@@ -15264,14 +15261,14 @@
         <v>19</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y112" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="Z112" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="Z112" t="s" s="2">
-        <v>611</v>
-      </c>
       <c r="AA112" t="s" s="2">
         <v>19</v>
       </c>
@@ -15288,7 +15285,7 @@
         <v>19</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -15314,10 +15311,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15340,17 +15337,17 @@
         <v>19</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>19</v>
@@ -15399,7 +15396,7 @@
         <v>19</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -15425,10 +15422,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15451,17 +15448,17 @@
         <v>19</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>19</v>
@@ -15510,7 +15507,7 @@
         <v>19</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15536,10 +15533,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15562,17 +15559,17 @@
         <v>19</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>19</v>
@@ -15621,7 +15618,7 @@
         <v>19</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15647,10 +15644,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15673,13 +15670,13 @@
         <v>19</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15730,40 +15727,40 @@
         <v>19</v>
       </c>
       <c r="AF116" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI116" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI116" t="s" s="2">
+      <c r="AJ116" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM116" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -15785,13 +15782,13 @@
         <v>134</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M117" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="N117" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15841,7 +15838,7 @@
         <v>19</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -15862,19 +15859,19 @@
         <v>19</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -15896,16 +15893,16 @@
         <v>134</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M118" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N118" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O118" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>19</v>
@@ -15954,7 +15951,7 @@
         <v>19</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15980,10 +15977,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16006,17 +16003,17 @@
         <v>19</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>19</v>
@@ -16065,7 +16062,7 @@
         <v>19</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>87</v>
@@ -16091,10 +16088,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16117,17 +16114,17 @@
         <v>19</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>19</v>
@@ -16176,7 +16173,7 @@
         <v>19</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -16202,10 +16199,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16228,17 +16225,17 @@
         <v>19</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>19</v>
@@ -16287,7 +16284,7 @@
         <v>19</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -16313,10 +16310,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16339,17 +16336,17 @@
         <v>19</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>19</v>
@@ -16398,7 +16395,7 @@
         <v>19</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -16424,10 +16421,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16450,17 +16447,17 @@
         <v>19</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>19</v>
@@ -16509,7 +16506,7 @@
         <v>19</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -16535,10 +16532,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16561,17 +16558,17 @@
         <v>19</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>19</v>
@@ -16620,7 +16617,7 @@
         <v>19</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -16646,10 +16643,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16672,17 +16669,17 @@
         <v>19</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>19</v>
@@ -16707,14 +16704,14 @@
         <v>19</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y125" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="Z125" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="Z125" t="s" s="2">
-        <v>655</v>
-      </c>
       <c r="AA125" t="s" s="2">
         <v>19</v>
       </c>
@@ -16731,7 +16728,7 @@
         <v>19</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16757,10 +16754,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16783,19 +16780,19 @@
         <v>19</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>19</v>
@@ -16820,14 +16817,14 @@
         <v>19</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="Z126" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="Z126" t="s" s="2">
-        <v>662</v>
-      </c>
       <c r="AA126" t="s" s="2">
         <v>19</v>
       </c>
@@ -16844,7 +16841,7 @@
         <v>19</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -16870,14 +16867,14 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -16896,19 +16893,19 @@
         <v>19</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>19</v>
@@ -16933,14 +16930,14 @@
         <v>19</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y127" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="Z127" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="Z127" t="s" s="2">
-        <v>670</v>
-      </c>
       <c r="AA127" t="s" s="2">
         <v>19</v>
       </c>
@@ -16957,7 +16954,7 @@
         <v>19</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
@@ -16983,14 +16980,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17009,13 +17006,13 @@
         <v>19</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17042,29 +17039,29 @@
         <v>19</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF128" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -17090,10 +17087,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17116,17 +17113,17 @@
         <v>19</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>19</v>
@@ -17175,7 +17172,7 @@
         <v>19</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -17201,10 +17198,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17227,19 +17224,19 @@
         <v>19</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="N130" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="N130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>19</v>
@@ -17264,14 +17261,14 @@
         <v>19</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y130" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="Z130" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="Z130" t="s" s="2">
-        <v>686</v>
-      </c>
       <c r="AA130" t="s" s="2">
         <v>19</v>
       </c>
@@ -17288,7 +17285,7 @@
         <v>19</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -17314,10 +17311,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17340,19 +17337,19 @@
         <v>19</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>19</v>
@@ -17377,14 +17374,14 @@
         <v>19</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y131" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="Z131" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="Z131" t="s" s="2">
-        <v>693</v>
-      </c>
       <c r="AA131" t="s" s="2">
         <v>19</v>
       </c>
@@ -17401,7 +17398,7 @@
         <v>19</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17427,10 +17424,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17453,17 +17450,17 @@
         <v>19</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>19</v>
@@ -17512,7 +17509,7 @@
         <v>19</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17530,7 +17527,7 @@
         <v>19</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>19</v>
@@ -17538,10 +17535,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17564,17 +17561,17 @@
         <v>19</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>19</v>
@@ -17599,14 +17596,14 @@
         <v>19</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y133" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="Z133" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="Z133" t="s" s="2">
-        <v>704</v>
-      </c>
       <c r="AA133" t="s" s="2">
         <v>19</v>
       </c>
@@ -17623,7 +17620,7 @@
         <v>19</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17641,7 +17638,7 @@
         <v>19</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>19</v>
@@ -17649,10 +17646,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17675,17 +17672,17 @@
         <v>19</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>19</v>
@@ -17734,7 +17731,7 @@
         <v>19</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17760,10 +17757,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17786,17 +17783,17 @@
         <v>19</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>19</v>
@@ -17845,7 +17842,7 @@
         <v>19</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17871,10 +17868,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17897,17 +17894,17 @@
         <v>19</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>19</v>
@@ -17956,7 +17953,7 @@
         <v>19</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -17982,10 +17979,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18008,19 +18005,19 @@
         <v>19</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>19</v>
@@ -18069,7 +18066,7 @@
         <v>19</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -18095,10 +18092,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18121,17 +18118,17 @@
         <v>19</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>19</v>
@@ -18180,7 +18177,7 @@
         <v>19</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -18206,10 +18203,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18232,19 +18229,19 @@
         <v>19</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>727</v>
       </c>
-      <c r="N139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>19</v>
@@ -18293,7 +18290,7 @@
         <v>19</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -18319,10 +18316,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18345,17 +18342,17 @@
         <v>19</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>19</v>
@@ -18404,7 +18401,7 @@
         <v>19</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -18430,10 +18427,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18456,13 +18453,13 @@
         <v>19</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18513,7 +18510,7 @@
         <v>19</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -18539,10 +18536,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18565,13 +18562,13 @@
         <v>19</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -18622,40 +18619,40 @@
         <v>19</v>
       </c>
       <c r="AF142" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI142" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI142" t="s" s="2">
+      <c r="AJ142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM142" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -18677,13 +18674,13 @@
         <v>134</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M143" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="N143" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -18733,7 +18730,7 @@
         <v>19</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
@@ -18754,19 +18751,19 @@
         <v>19</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -18788,16 +18785,16 @@
         <v>134</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M144" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N144" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O144" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>19</v>
@@ -18846,7 +18843,7 @@
         <v>19</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
@@ -18872,10 +18869,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18898,19 +18895,19 @@
         <v>19</v>
       </c>
       <c r="K145" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="L145" t="s" s="2">
         <v>738</v>
       </c>
-      <c r="L145" t="s" s="2">
+      <c r="M145" t="s" s="2">
         <v>739</v>
       </c>
-      <c r="M145" t="s" s="2">
+      <c r="N145" t="s" s="2">
         <v>740</v>
       </c>
-      <c r="N145" t="s" s="2">
+      <c r="O145" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>742</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>19</v>
@@ -18935,11 +18932,11 @@
         <v>19</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y145" s="2"/>
       <c r="Z145" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>19</v>
@@ -18957,7 +18954,7 @@
         <v>19</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>87</v>
@@ -18983,10 +18980,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19009,17 +19006,17 @@
         <v>19</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>19</v>
@@ -19044,11 +19041,11 @@
         <v>19</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y146" s="2"/>
       <c r="Z146" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>19</v>
@@ -19066,7 +19063,7 @@
         <v>19</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -19092,10 +19089,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19118,19 +19115,19 @@
         <v>19</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="N147" t="s" s="2">
+      <c r="O147" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>19</v>
@@ -19179,7 +19176,7 @@
         <v>19</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -19194,7 +19191,7 @@
         <v>99</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>19</v>
@@ -19205,10 +19202,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19231,17 +19228,17 @@
         <v>19</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>19</v>
@@ -19290,7 +19287,7 @@
         <v>19</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -19316,10 +19313,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19342,13 +19339,13 @@
         <v>19</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L149" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="M149" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -19399,40 +19396,40 @@
         <v>19</v>
       </c>
       <c r="AF149" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI149" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI149" t="s" s="2">
+      <c r="AJ149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM149" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK149" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL149" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -19454,13 +19451,13 @@
         <v>134</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M150" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="N150" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19510,7 +19507,7 @@
         <v>19</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -19531,19 +19528,19 @@
         <v>19</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -19565,16 +19562,16 @@
         <v>134</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M151" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N151" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O151" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>19</v>
@@ -19623,7 +19620,7 @@
         <v>19</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
@@ -19649,10 +19646,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19675,17 +19672,17 @@
         <v>19</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>19</v>
@@ -19734,7 +19731,7 @@
         <v>19</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>87</v>
@@ -19760,10 +19757,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19786,17 +19783,17 @@
         <v>19</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>19</v>
@@ -19845,7 +19842,7 @@
         <v>19</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
@@ -19871,10 +19868,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19897,17 +19894,17 @@
         <v>19</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>19</v>
@@ -19932,14 +19929,14 @@
         <v>19</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y154" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="Z154" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="Z154" t="s" s="2">
-        <v>655</v>
-      </c>
       <c r="AA154" t="s" s="2">
         <v>19</v>
       </c>
@@ -19956,7 +19953,7 @@
         <v>19</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
@@ -19982,10 +19979,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20008,19 +20005,19 @@
         <v>19</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="N155" t="s" s="2">
+      <c r="O155" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>19</v>
@@ -20045,14 +20042,14 @@
         <v>19</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y155" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="Z155" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="Z155" t="s" s="2">
-        <v>662</v>
-      </c>
       <c r="AA155" t="s" s="2">
         <v>19</v>
       </c>
@@ -20069,7 +20066,7 @@
         <v>19</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
@@ -20095,14 +20092,14 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -20121,19 +20118,19 @@
         <v>19</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="N156" t="s" s="2">
+      <c r="O156" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>19</v>
@@ -20158,14 +20155,14 @@
         <v>19</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y156" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="Z156" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="Z156" t="s" s="2">
-        <v>670</v>
-      </c>
       <c r="AA156" t="s" s="2">
         <v>19</v>
       </c>
@@ -20182,7 +20179,7 @@
         <v>19</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
@@ -20208,14 +20205,14 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
@@ -20234,13 +20231,13 @@
         <v>19</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -20267,11 +20264,11 @@
         <v>19</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y157" s="2"/>
       <c r="Z157" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>19</v>
@@ -20289,7 +20286,7 @@
         <v>19</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
@@ -20315,10 +20312,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20341,19 +20338,19 @@
         <v>19</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="N158" t="s" s="2">
         <v>762</v>
       </c>
-      <c r="M158" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>763</v>
-      </c>
       <c r="O158" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>19</v>
@@ -20378,14 +20375,14 @@
         <v>19</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y158" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="Z158" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="Z158" t="s" s="2">
-        <v>686</v>
-      </c>
       <c r="AA158" t="s" s="2">
         <v>19</v>
       </c>
@@ -20402,7 +20399,7 @@
         <v>19</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>76</v>
@@ -20428,10 +20425,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20454,19 +20451,19 @@
         <v>19</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="N159" t="s" s="2">
+      <c r="O159" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>19</v>
@@ -20491,14 +20488,14 @@
         <v>19</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y159" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="Z159" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="Z159" t="s" s="2">
-        <v>693</v>
-      </c>
       <c r="AA159" t="s" s="2">
         <v>19</v>
       </c>
@@ -20515,7 +20512,7 @@
         <v>19</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -20541,10 +20538,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20567,17 +20564,17 @@
         <v>19</v>
       </c>
       <c r="K160" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="L160" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="L160" t="s" s="2">
+      <c r="M160" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>19</v>
@@ -20626,7 +20623,7 @@
         <v>19</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -20652,10 +20649,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20678,17 +20675,17 @@
         <v>19</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="L161" t="s" s="2">
+      <c r="M161" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>19</v>
@@ -20737,7 +20734,7 @@
         <v>19</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -20763,10 +20760,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20789,17 +20786,17 @@
         <v>19</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>19</v>
@@ -20848,7 +20845,7 @@
         <v>19</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -20874,10 +20871,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20900,19 +20897,19 @@
         <v>19</v>
       </c>
       <c r="K163" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="L163" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="L163" t="s" s="2">
+      <c r="M163" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="N163" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="N163" t="s" s="2">
+      <c r="O163" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>19</v>
@@ -20961,7 +20958,7 @@
         <v>19</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>76</v>
@@ -20987,10 +20984,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21013,17 +21010,17 @@
         <v>19</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>19</v>
@@ -21072,7 +21069,7 @@
         <v>19</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
@@ -21098,10 +21095,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21124,19 +21121,19 @@
         <v>19</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="N165" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="O165" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>19</v>
@@ -21185,7 +21182,7 @@
         <v>19</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>76</v>
@@ -21211,10 +21208,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21237,17 +21234,17 @@
         <v>19</v>
       </c>
       <c r="K166" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L166" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L166" t="s" s="2">
+      <c r="M166" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>19</v>
@@ -21296,7 +21293,7 @@
         <v>19</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>76</v>
@@ -21322,10 +21319,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21348,17 +21345,17 @@
         <v>19</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>19</v>
@@ -21407,7 +21404,7 @@
         <v>19</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>76</v>
@@ -21433,10 +21430,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21459,13 +21456,13 @@
         <v>19</v>
       </c>
       <c r="K168" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L168" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L168" t="s" s="2">
+      <c r="M168" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -21516,40 +21513,40 @@
         <v>19</v>
       </c>
       <c r="AF168" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH168" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI168" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG168" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH168" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI168" t="s" s="2">
+      <c r="AJ168" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL168" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM168" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AJ168" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK168" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL168" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM168" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -21571,13 +21568,13 @@
         <v>134</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M169" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="N169" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -21627,7 +21624,7 @@
         <v>19</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -21648,19 +21645,19 @@
         <v>19</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
@@ -21682,16 +21679,16 @@
         <v>134</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M170" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="N170" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O170" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>19</v>
@@ -21740,7 +21737,7 @@
         <v>19</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
@@ -21766,10 +21763,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21792,17 +21789,17 @@
         <v>19</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>19</v>
@@ -21851,7 +21848,7 @@
         <v>19</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>87</v>
@@ -21877,10 +21874,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21903,17 +21900,17 @@
         <v>19</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>19</v>
@@ -21962,7 +21959,7 @@
         <v>19</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>76</v>
@@ -21988,10 +21985,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22014,17 +22011,17 @@
         <v>19</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>19</v>
@@ -22049,14 +22046,14 @@
         <v>19</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y173" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="Z173" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="Z173" t="s" s="2">
-        <v>655</v>
-      </c>
       <c r="AA173" t="s" s="2">
         <v>19</v>
       </c>
@@ -22073,7 +22070,7 @@
         <v>19</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>76</v>
@@ -22099,10 +22096,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22125,19 +22122,19 @@
         <v>19</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="N174" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="N174" t="s" s="2">
+      <c r="O174" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="O174" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>19</v>
@@ -22162,14 +22159,14 @@
         <v>19</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y174" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="Z174" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="Z174" t="s" s="2">
-        <v>662</v>
-      </c>
       <c r="AA174" t="s" s="2">
         <v>19</v>
       </c>
@@ -22186,7 +22183,7 @@
         <v>19</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>76</v>
@@ -22212,10 +22209,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22238,19 +22235,19 @@
         <v>19</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="N175" t="s" s="2">
+      <c r="O175" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>19</v>
@@ -22275,14 +22272,14 @@
         <v>19</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y175" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="Z175" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="Z175" t="s" s="2">
-        <v>670</v>
-      </c>
       <c r="AA175" t="s" s="2">
         <v>19</v>
       </c>
@@ -22299,7 +22296,7 @@
         <v>19</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -22325,14 +22322,14 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -22351,13 +22348,13 @@
         <v>19</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -22384,11 +22381,11 @@
         <v>19</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>19</v>
@@ -22406,7 +22403,7 @@
         <v>19</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>76</v>
@@ -22432,10 +22429,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22458,19 +22455,19 @@
         <v>19</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M177" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="N177" t="s" s="2">
         <v>762</v>
       </c>
-      <c r="M177" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>763</v>
-      </c>
       <c r="O177" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>19</v>
@@ -22495,14 +22492,14 @@
         <v>19</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y177" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="Z177" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="Z177" t="s" s="2">
-        <v>686</v>
-      </c>
       <c r="AA177" t="s" s="2">
         <v>19</v>
       </c>
@@ -22519,7 +22516,7 @@
         <v>19</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>76</v>
@@ -22545,10 +22542,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22571,19 +22568,19 @@
         <v>19</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M178" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="N178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>19</v>
@@ -22608,14 +22605,14 @@
         <v>19</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y178" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="Z178" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="Z178" t="s" s="2">
-        <v>693</v>
-      </c>
       <c r="AA178" t="s" s="2">
         <v>19</v>
       </c>
@@ -22632,7 +22629,7 @@
         <v>19</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>76</v>
@@ -22658,10 +22655,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22684,17 +22681,17 @@
         <v>19</v>
       </c>
       <c r="K179" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="L179" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="L179" t="s" s="2">
+      <c r="M179" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>19</v>
@@ -22743,7 +22740,7 @@
         <v>19</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>76</v>
@@ -22769,10 +22766,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22795,17 +22792,17 @@
         <v>19</v>
       </c>
       <c r="K180" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="L180" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="L180" t="s" s="2">
+      <c r="M180" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>19</v>
@@ -22854,7 +22851,7 @@
         <v>19</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>76</v>
@@ -22880,10 +22877,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22906,17 +22903,17 @@
         <v>19</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>19</v>
@@ -22965,7 +22962,7 @@
         <v>19</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
@@ -22991,10 +22988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23017,19 +23014,19 @@
         <v>19</v>
       </c>
       <c r="K182" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="L182" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="L182" t="s" s="2">
+      <c r="M182" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="M182" t="s" s="2">
+      <c r="N182" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="N182" t="s" s="2">
+      <c r="O182" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>19</v>
@@ -23078,7 +23075,7 @@
         <v>19</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>76</v>
@@ -23104,10 +23101,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23130,17 +23127,17 @@
         <v>19</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>19</v>
@@ -23189,7 +23186,7 @@
         <v>19</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>76</v>
@@ -23215,10 +23212,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23241,19 +23238,19 @@
         <v>19</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="N184" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="O184" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>19</v>
@@ -23302,7 +23299,7 @@
         <v>19</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>76</v>
@@ -23328,10 +23325,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23354,17 +23351,17 @@
         <v>19</v>
       </c>
       <c r="K185" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L185" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L185" t="s" s="2">
+      <c r="M185" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>19</v>
@@ -23413,7 +23410,7 @@
         <v>19</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>76</v>
@@ -23439,10 +23436,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23465,17 +23462,17 @@
         <v>19</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="M186" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>19</v>
@@ -23524,7 +23521,7 @@
         <v>19</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>76</v>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedLKFRequest</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedLKFRequest</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,19 +54,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -477,7 +477,7 @@
     <t>DiagnoseKnoten</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-diagnoseKnoten}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-diagnoseKnoten}
 </t>
   </si>
   <si>
@@ -490,7 +490,7 @@
     <t>LKFPunkte</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-LKFPunkte}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-LKFPunkte}
 </t>
   </si>
   <si>
@@ -506,7 +506,7 @@
     <t>FehlerWarnung</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-fehlerWarnung}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-fehlerWarnung}
 </t>
   </si>
   <si>
@@ -522,7 +522,7 @@
     <t>Fondsrelevanz</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-fondsrelevanz}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-fondsrelevanz}
 </t>
   </si>
   <si>
@@ -535,7 +535,7 @@
     <t>Plausibilitaetskennzeichen</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/Plausibilitaetskennzeichen}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/Plausibilitaetskennzeichen}
 </t>
   </si>
   <si>
@@ -548,7 +548,7 @@
     <t>SVAbrechnungsquartal</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/SVAbrechnungsquartal}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/SVAbrechnungsquartal}
 </t>
   </si>
   <si>
@@ -975,7 +975,7 @@
     <t>Claim.related.claim</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedLKFRequest)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedLKFRequest)
 </t>
   </si>
   <si>
@@ -1167,7 +1167,7 @@
     <t>MopedEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedEncounter)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedEncounter)
 </t>
   </si>
   <si>
@@ -1180,7 +1180,7 @@
     <t>TransferEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedTransferEncounter)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedTransferEncounter)
 </t>
   </si>
   <si>
@@ -1221,7 +1221,7 @@
     <t>Required to relate the current diagnosis to a package billing code that is then referenced on the individual claim items which are specific to the health condition covered by the package code.</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-LKFAbrechnungsGruppe-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-LKFAbrechnungsGruppe-valueset</t>
   </si>
   <si>
     <t>Claim.event</t>
@@ -1640,7 +1640,7 @@
     <t>AbrechnungsRelevanz</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-AbrechnungsRelevanz}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-AbrechnungsRelevanz}
 </t>
   </si>
   <si>
@@ -1802,7 +1802,7 @@
     <t>Claim.insurance.coverage</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedCoverage)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedCoverage)
 </t>
   </si>
   <si>
@@ -2808,7 +2808,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.6484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.26953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:36:14+00:00</t>
+    <t>2025-02-20T20:13:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1221,7 +1221,7 @@
     <t>Required to relate the current diagnosis to a package billing code that is then referenced on the individual claim items which are specific to the health condition covered by the package code.</t>
   </si>
   <si>
-    <t>https://elga.moped.at/ValueSet/moped-LKFAbrechnungsGruppe-valueset</t>
+    <t>https://elga.moped.at/ValueSet/LKFAbrechnungsGruppe</t>
   </si>
   <si>
     <t>Claim.event</t>
@@ -2808,7 +2808,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.6484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.4765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
